--- a/data/trans_orig/cron_mort_index-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/cron_mort_index-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de cronicidad física en base a la mortalidad</t>
+          <t>Índice de cronicidad física en base a la mortalidad (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,08</t>
+          <t>0,04; 0,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,25</t>
+          <t>0,09; 0,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,09</t>
+          <t>0,06; 0,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,1</t>
+          <t>0,06; 0,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,22</t>
+          <t>0,11; 0,21</t>
         </is>
       </c>
     </row>
@@ -1141,37 +1141,37 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0,09; 0,13</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,07; 0,11</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,21; 0,28</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,05; 0,08</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,11; 0,15</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>0,09; 0,14</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,11</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,21; 0,27</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,05; 0,08</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,11; 0,15</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 0,13</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,41</t>
+          <t>0,22; 0,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,14</t>
+          <t>0,1; 0,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,37</t>
+          <t>0,23; 0,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/cron_mort_index-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/cron_mort_index-Habitat-trans_orig.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,25</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,07</t>
+          <t>0,04; 0,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,26</t>
+          <t>0,21; 0,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,27</t>
+          <t>0,22; 0,27</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,22</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,11</t>
+          <t>0,08; 0,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,25</t>
+          <t>0,2; 0,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,24</t>
+          <t>0,19; 0,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,08</t>
+          <t>0,06; 0,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,23</t>
+          <t>0,2; 0,24</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>0,2</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,28</t>
+          <t>0,19; 0,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,12</t>
+          <t>0,08; 0,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,19</t>
+          <t>0,16; 0,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,21</t>
+          <t>0,18; 0,23</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,24</t>
         </is>
       </c>
     </row>
@@ -1141,37 +1141,37 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0,09; 0,14</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,07; 0,11</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,21; 0,27</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,05; 0,08</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,11; 0,15</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>0,09; 0,13</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 0,11</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,21; 0,28</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,05; 0,08</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,11; 0,15</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0,09; 0,14</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,43</t>
+          <t>0,21; 0,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,14</t>
+          <t>0,11; 0,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,36</t>
+          <t>0,22; 0,26</t>
         </is>
       </c>
     </row>
@@ -1223,47 +1223,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>0,24</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,07</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0,11</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0,22</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>0,1</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>0,1</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,23</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,25</t>
+          <t>0,22; 0,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,26</t>
+          <t>0,2; 0,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,25</t>
+          <t>0,22; 0,24</t>
         </is>
       </c>
     </row>
